--- a/roofing-leads/leads.xlsx
+++ b/roofing-leads/leads.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Leads'!$A$1:$M$179</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phone Only'!$A$1:$M$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Leads'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Phone Only'!$A$1:$M$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3223,7 +3223,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Integrity Rise Management (Patriot Woods / Patriot on the Trace)</t>
+          <t>Alfonso Property Management / Coldwell Banker Commercial Alfonso Realty</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Long Ave</t>
+          <t>934 Jackson Ave</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3241,14 +3241,26 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>39567</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>(228) 818-5788</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>alfonsopm.com</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Manages several Pascagoula apartment complexes; no email found; Source: web search - https://homefinder.com/apartments/Helena_MS/sby-6</t>
+          <t>Residential + commercial property management and commercial leasing; brokers for Jackson Square (Gautier); no email found; Source: web search - https://alfonsopmjacksoncounty.property-genie.com/</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3262,7 +3274,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Smith Gary Realty</t>
+          <t>Dantzler Management</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3272,7 +3284,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1964 Market St</t>
+          <t>3207 Frederic St</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3281,13 +3293,17 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>(228) 762-4611</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.simplifyem.com/property-management-companies/company/smith-gary-realty-pascagoula-mississippi</t>
+          <t>In business 55 years per Yellow Pages; no email found; Source: web search - https://www.yellowpages.com/pascagoula-ms/property-management</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3301,17 +3317,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cornerstone Restaurant</t>
+          <t>Dronet Realty &amp; Property Management</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Property Management</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1740 Denny Ave</t>
+          <t>1741 Jackson Ave</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3324,13 +3340,17 @@
           <t>39567</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>(228) 447-3727</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
+          <t>Residential, commercial and land management; no email found; Source: web search - https://www.facebook.com/dronetrealty/</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3344,17 +3364,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Edd's Drive In</t>
+          <t>Integrity Rise Management (Patriot Woods / Patriot on the Trace)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Property Management</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3834 Market St</t>
+          <t>Long Ave</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3362,18 +3382,14 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
+          <t>Manages Patriot Woods (4800 Long Ave), Patriot Orchard (5111 Orchard), Patriot Gardens, Patriot Pointe, Patriot on the Trace - one contact for several complexes; central office phone not found; no email found; Source: web search - https://homefinder.com/apartments/Helena_MS/sby-6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3387,36 +3403,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Frets Live Music and Eatery</t>
+          <t>Ms Gulf Coast Rental Properties</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Restaurant</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>702 Delmas Ave</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
+          <t>Named in Pascagoula property management directory; address/phone not shown; no email found; Source: web search - https://www.yellowpages.com/pascagoula-ms/property-management</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3430,19 +3438,15 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>McAlister's Deli</t>
+          <t>Revitalize Realty</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Restaurant</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>4101 Hospital Rd</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>Pascagoula</t>
@@ -3455,7 +3459,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://archive.schulershook.com/mcalisters-pascagoula-mississippi.pdf</t>
+          <t>Named in Pascagoula property management directory; address/phone not shown; no email found; Source: web search - https://www.yellowpages.com/pascagoula-ms/property-management</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3469,36 +3473,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>New York Pizza</t>
+          <t>Seaman &amp; Associates</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Restaurant</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2415 Market St</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://trunking.opensips.org/new-york-pizza-in-pascagoula-ms.html</t>
+          <t>Named in Pascagoula property management directory; address/phone not shown; no email found; Source: web search - https://www.yellowpages.com/pascagoula-ms/property-management</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3512,17 +3508,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Paradise Deli &amp; Grill</t>
+          <t>Smith Gary Realty</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Property Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>610 Delmas Ave</t>
+          <t>1964 Market St</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3530,18 +3526,14 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
+          <t>no email found; Source: web search - https://www.simplifyem.com/property-management-companies/company/smith-gary-realty-pascagoula-mississippi</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3555,7 +3547,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Scranton's Restaurant and Catering</t>
+          <t>Cornerstone Restaurant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3565,7 +3557,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>623 Delmas Ave</t>
+          <t>1740 Denny Ave</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3598,7 +3590,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Yamato</t>
+          <t>Edd's Drive In</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3608,7 +3600,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2409 Market St</t>
+          <t>3834 Market St</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3641,17 +3633,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Frets Live Music and Eatery</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3400 Chicot St</t>
+          <t>702 Delmas Ave</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3661,20 +3653,16 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>39581</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>(228) 762-8660</t>
-        </is>
-      </c>
+          <t>39567</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
+          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3688,17 +3676,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ice House Retail Center</t>
+          <t>McAlister's Deli</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1005 Denny Ave</t>
+          <t>4101 Hospital Rd</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3713,7 +3701,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Newer multi-tenant retail development; no email found; Source: web search - https://www.commercialsearch.com/commercial-property/us/ms/pascagoula/the-ice-house-retail-center/</t>
+          <t>no email found; Source: web search - https://archive.schulershook.com/mcalisters-pascagoula-mississippi.pdf</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3727,17 +3715,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NAPA Auto Parts</t>
+          <t>New York Pizza</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4009 14th St</t>
+          <t>2415 Market St</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3750,17 +3738,13 @@
           <t>39567</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>(228) 762-1344</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
+          <t>no email found; Source: web search - https://trunking.opensips.org/new-york-pizza-in-pascagoula-ms.html</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3774,17 +3758,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Strip center - 3806 Hospital Rd</t>
+          <t>Paradise Deli &amp; Grill</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3806 Hospital Rd</t>
+          <t>610 Delmas Ave</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3792,14 +3776,18 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>39567</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Retail/office strip next to Pizza Hut; for-lease listing; no email found; Source: web search - https://www.commercialsearch.com/commercial-property/us/ms/pascagoula/office-for-sale</t>
+          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3813,17 +3801,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Arlington Elementary</t>
+          <t>Scranton's Restaurant and Catering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3511 Arlington St</t>
+          <t>623 Delmas Ave</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3833,20 +3821,16 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>39581</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>(228) 938-6552</t>
-        </is>
-      </c>
+          <t>39567</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
+          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3860,17 +3844,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Beach Elementary</t>
+          <t>Yamato</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>633 Market St</t>
+          <t>2409 Market St</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3889,7 +3873,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
+          <t>no email found; Source: web search - https://app.foursquare.com/user/4521840/list/guide-to-pascagoulas-best-spots</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -3903,17 +3887,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Central Elementary</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1100 Dupont St</t>
+          <t>3400 Chicot St</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3923,16 +3907,20 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>39567</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>39581</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>(228) 762-8660</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
+          <t>National chain; no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3946,17 +3934,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cherokee Elementary</t>
+          <t>Ice House Retail Center</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4102 Scovel Rd</t>
+          <t>1005 Denny Ave</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3964,18 +3952,14 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>39581</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
+          <t>Newer multi-tenant retail development; no email found; Source: web search - https://www.commercialsearch.com/commercial-property/us/ms/pascagoula/the-ice-house-retail-center/</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -3989,17 +3973,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jackson Elementary</t>
+          <t>NAPA Auto Parts</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3203 Lanier St</t>
+          <t>4009 14th St</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4007,10 +3991,14 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>39567</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>(228) 938-6554</t>
+          <t>(228) 762-1344</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4018,7 +4006,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Closing after 2025-26 school year; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39567/search.aspx</t>
+          <t>no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4032,17 +4020,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lake Elementary</t>
+          <t>Strip center - 3806 Hospital Rd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4503 Willow St</t>
+          <t>3806 Hospital Rd</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4050,18 +4038,14 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
+          <t>Retail/office strip next to Pizza Hut; for-lease listing; no email found; Source: web search - https://www.commercialsearch.com/commercial-property/us/ms/pascagoula/office-for-sale</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4075,7 +4059,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pascagoula Opportunity Center</t>
+          <t>Arlington Elementary</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4085,7 +4069,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1520 Tucker Ave</t>
+          <t>3511 Arlington St</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4095,10 +4079,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>39567</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+          <t>39581</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>(228) 938-6552</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -4118,7 +4106,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier School District Central Office</t>
+          <t>Beach Elementary</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4128,7 +4116,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1006 Communy Ave</t>
+          <t>633 Market St</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4144,14 +4132,10 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>pgsd.ms</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>District facilities dept handles all ~19 campuses; no email found; Source: web search - https://en.wikipedia.org/wiki/Pascagoula-Gautier_School_District</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4165,17 +4149,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Belair Storage</t>
+          <t>Central Elementary</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3011 Belair St</t>
+          <t>1100 Dupont St</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4194,7 +4178,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.neighbor.com/facility/mississippi/pascagoula/belair-storage/3011-belair-st/16360</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4208,17 +4192,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BIG Storage Pascagoula</t>
+          <t>Cherokee Elementary</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3503 Lanier Ave</t>
+          <t>4102 Scovel Rd</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4237,7 +4221,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4251,17 +4235,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Central Self Storage</t>
+          <t>Jackson Elementary</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2902 Bartlett Ave</t>
+          <t>3203 Lanier St</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4269,18 +4253,18 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>(228) 938-6554</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
+          <t>Closing after 2025-26 school year; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39567/search.aspx</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4294,17 +4278,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Coastal Life Storage</t>
+          <t>Lake Elementary</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2609 Bayou Cassotte Pkwy</t>
+          <t>4503 Willow St</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4323,7 +4307,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4337,17 +4321,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Handy Lock Self Storage - Pascagoula</t>
+          <t>Pascagoula Opportunity Center</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1710 Market St</t>
+          <t>1520 Tucker Ave</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4366,7 +4350,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4380,17 +4364,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Radiant Storage Pascagoula</t>
+          <t>Pascagoula-Gautier School District Central Office</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4203 Nathan Hale Ave</t>
+          <t>1006 Communy Ave</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4398,14 +4382,22 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>39567</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pgsd.ms</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
+          <t>District facilities dept handles all ~19 campuses; no email found; Source: web search - https://en.wikipedia.org/wiki/Pascagoula-Gautier_School_District</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -4419,7 +4411,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Storage Choice</t>
+          <t>Belair Storage</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4429,7 +4421,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3326 Market St</t>
+          <t>3011 Belair St</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4448,7 +4440,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
+          <t>no email found; Source: web search - https://www.neighbor.com/facility/mississippi/pascagoula/belair-storage/3011-belair-st/16360</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4462,7 +4454,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>U-Haul Storage of Pascagoula</t>
+          <t>BIG Storage Pascagoula</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4472,7 +4464,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2903 Shortcut Rd</t>
+          <t>3503 Lanier Ave</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4482,20 +4474,16 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>39567</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>uhaul.com</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.neighbor.com/facility/mississippi/pascagoula/u-haul-storage-of-pascagoula/2903-shortcut-rd/12836</t>
+          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4509,17 +4497,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Industrial warehouse - 5002 Bayou Cassotte Pkwy</t>
+          <t>Central Self Storage</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5002 Bayou Cassotte Pkwy</t>
+          <t>2902 Bartlett Ave</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4529,7 +4517,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -4538,7 +4526,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>~13,768 SF; for sale; no email found; Source: web search - https://commercial.century21.com/listing/5002-bayou-cassotte-parkway-pascagoula-ms-39581-REN027804677</t>
+          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4552,17 +4540,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Port Pascagoula (Jackson County Port Authority)</t>
+          <t>Coastal Life Storage</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PO Box 70</t>
+          <t>2609 Bayou Cassotte Pkwy</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4572,32 +4560,16 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>39568</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>(228) 762-4041</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>info@portofpascagoula.com</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>https://www.cogoport.com/knowledge-center/resources/port-info/pascagoula</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>portofpascagoula.com</t>
-        </is>
-      </c>
+          <t>39567</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Port warehousing; mailing address only; email from shipping directory (not port website) - verify; Source: web search - https://mdot.ms.gov/ports/pascagoula.html</t>
+          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -4611,17 +4583,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Warehouse - 2205 Petit Bois St</t>
+          <t>Handy Lock Self Storage - Pascagoula</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2205 Petit Bois St</t>
+          <t>1710 Market St</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4631,20 +4603,16 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>39581</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>(228) 365-8763</t>
-        </is>
-      </c>
+          <t>39567</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>For sale; phone is listing contact; no email found; Source: web search - https://www.showcase.com/2205-petit-bois-st-pascagoula-ms-39581/35200689/</t>
+          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4658,40 +4626,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ante Bellum Manor (condos)</t>
+          <t>Radiant Storage Pascagoula</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Apartment Complex</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>5080 Gautier Vancleave Rd</t>
+          <t>4203 Nathan Hale Ave</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Gautier</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>(228) 447-3727</t>
-        </is>
-      </c>
+          <t>Pascagoula</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Phone is from a unit rental listing; no email found; Source: web search - https://www.apartments.com/5080-gautier-vancleave-rd-gautier-ms/58b795p/</t>
+          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -4705,27 +4665,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bayou Village Apartments</t>
+          <t>Storage Choice</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Apartment Complex</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>off Martin Bluff Rd</t>
+          <t>3326 Market St</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4734,7 +4694,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://hotpads.com/bayou-village-gautier-ms-39553-srzv5x/pad</t>
+          <t>no email found; Source: web search - https://www.sparefoot.com/pascagoula-ms-self-storage.html</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4748,40 +4708,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Firestone Complete Auto Care - Gautier</t>
+          <t>U-Haul Storage of Pascagoula</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3299 Old Spanish Trail</t>
+          <t>2903 Shortcut Rd</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>39553</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>(228) 497-7014</t>
-        </is>
-      </c>
+          <t>39567</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>uhaul.com</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.kbb.com/service-centers/gautier-ms</t>
+          <t>National chain; no email found; Source: web search - https://www.neighbor.com/facility/mississippi/pascagoula/u-haul-storage-of-pascagoula/2903-shortcut-rd/12836</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4795,27 +4755,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gautier Automotive</t>
+          <t>Industrial warehouse - 5002 Bayou Cassotte Pkwy</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3604 Hwy 90</t>
+          <t>5002 Bayou Cassotte Pkwy</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4824,7 +4784,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.kbb.com/service-centers/gautier-ms</t>
+          <t>~13,768 SF; for sale; no email found; Source: web search - https://commercial.century21.com/listing/5002-bayou-cassotte-parkway-pascagoula-ms-39581-REN027804677</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4838,36 +4798,52 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bethel Missionary Baptist Church</t>
+          <t>Port Pascagoula (Jackson County Port Authority)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1700 Ladnier Rd</t>
+          <t>PO Box 70</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>39553</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+          <t>39568</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>(228) 762-4041</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>info@portofpascagoula.com</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.cogoport.com/knowledge-center/resources/port-info/pascagoula</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>portofpascagoula.com</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://churcheslist.com/?p=144819</t>
+          <t>Port warehousing; mailing address only; email from shipping directory (not port website) - verify; Source: web search - https://mdot.ms.gov/ports/pascagoula.html</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4881,32 +4857,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Church of St. Mary (Catholic)</t>
+          <t>Warehouse - 2205 Petit Bois St</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>809 De La Pointe Dr</t>
+          <t>2205 Petit Bois St</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>(228) 497-2364</t>
+          <t>(228) 365-8763</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -4914,7 +4890,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30128</t>
+          <t>For sale; phone is listing contact; no email found; Source: web search - https://www.showcase.com/2205-petit-bois-st-pascagoula-ms-39581/35200689/</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -4928,17 +4904,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>First Baptist Church of Gautier</t>
+          <t>Ante Bellum Manor (condos)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Apartment Complex</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>325 De La Pointe Dr</t>
+          <t>5080 Gautier Vancleave Rd</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4951,13 +4927,17 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>(228) 447-3727</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.disciplepair.com/browse/church/first-baptist-church-of-gautier-gautier-ms</t>
+          <t>Phone is Dronet Realty &amp; Property Management (listing agent); no email found; Source: web search - https://www.apartments.com/5080-gautier-vancleave-rd-gautier-ms/58b795p/</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -4971,17 +4951,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gautier First United Methodist Church</t>
+          <t>Bayou Village Apartments</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Apartment Complex</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2717 Hwy 90</t>
+          <t>off Martin Bluff Rd</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4994,17 +4974,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>(228) 497-1698</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Phone from church directory search result - verify; no email found; Source: web search - https://feedam.org/resource/172621</t>
+          <t>no email found; Source: web search - https://hotpads.com/bayou-village-gautier-ms-39553-srzv5x/pad</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5018,17 +4994,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Providence Baptist Church</t>
+          <t>Firestone Complete Auto Care - Gautier</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2021 Ladnier Rd</t>
+          <t>3299 Old Spanish Trail</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5041,13 +5017,17 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>(228) 497-7014</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://churcheslist.com/?p=144837</t>
+          <t>National chain; no email found; Source: web search - https://www.kbb.com/service-centers/gautier-ms</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5061,17 +5041,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Restoration Apostolic Church</t>
+          <t>Gautier Automotive</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2101 Martin Bluff Rd</t>
+          <t>3604 Hwy 90</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5090,7 +5070,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://churcheslist.com/?p=121370</t>
+          <t>no email found; Source: web search - https://www.kbb.com/service-centers/gautier-ms</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5104,15 +5084,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gautier Commerce Center</t>
+          <t>Bethel Missionary Baptist Church</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1700 Ladnier Rd</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>Gautier</t>
@@ -5129,7 +5113,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>12-unit business condo complex; address not listed; no email found; Source: web search - https://www.wlox.com/2019/06/18/new-business-sets-up-shop-inside-gautier-purchase-only-complex/</t>
+          <t>no email found; Source: web search - https://churcheslist.com/?p=144819</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5143,17 +5127,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Magnolia Inn</t>
+          <t>Church of St. Mary (Catholic)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>704 Hwy 90</t>
+          <t>809 De La Pointe Dr</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5168,7 +5152,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>(228) 522-0288</t>
+          <t>(228) 497-2364</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -5176,7 +5160,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://allstays.com/hotels/32256.htm</t>
+          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30128</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5190,17 +5174,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Office/warehouse building - 3708 Hwy 90</t>
+          <t>First Baptist Church of Gautier</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3708 Hwy 90</t>
+          <t>325 De La Pointe Dr</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5219,7 +5203,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Freestanding office + 7,000 SF warehouse; for-lease listing; no email found; Source: web search - https://www.commercialsearch.com/commercial-property/us/ms/gautier/3708-highway-90-1/</t>
+          <t>no email found; Source: web search - https://www.disciplepair.com/browse/church/first-baptist-church-of-gautier-gautier-ms</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5233,17 +5217,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Two-story commercial complex - 2012 Hwy 90</t>
+          <t>Gautier First United Methodist Church</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2012 Hwy 90</t>
+          <t>2717 Hwy 90</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5256,13 +5240,17 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>(228) 497-1698</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>For-sale listing, 1.69 acres; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/gautier/2012-highway-90/</t>
+          <t>Phone from church directory search result - verify; no email found; Source: web search - https://feedam.org/resource/172621</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5276,17 +5264,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dental office of Dr. Angela Baudean, DMD</t>
+          <t>Providence Baptist Church</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>713 Hwy 90</t>
+          <t>2021 Ladnier Rd</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5299,17 +5287,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>(228) 201-3621</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-angela-baudean-d-m-d-gautier-ms</t>
+          <t>no email found; Source: web search - https://churcheslist.com/?p=144837</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5323,17 +5307,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dental office of Dr. Jeffrey Knight, DDS</t>
+          <t>Restoration Apostolic Church</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3105 Shaw Dr</t>
+          <t>2101 Martin Bluff Rd</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5346,17 +5330,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>(228) 497-3111</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-jeffrey-knight-d-d-s-gautier-ms</t>
+          <t>no email found; Source: web search - https://churcheslist.com/?p=121370</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -5370,19 +5350,15 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dental office of Dr. Michael Steward, DDS</t>
+          <t>Gautier Commerce Center</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Medical Office</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>4113 Gautier Vancleave Rd</t>
-        </is>
-      </c>
+          <t>Commercial Building</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>Gautier</t>
@@ -5393,21 +5369,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>(228) 497-1333</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>mikestewarddds.com</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-michael-steward-dds-gautier-ms</t>
+          <t>12-unit business condo complex; address not listed; no email found; Source: web search - https://www.wlox.com/2019/06/18/new-business-sets-up-shop-inside-gautier-purchase-only-complex/</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -5421,17 +5389,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Gautier Family Dental Care</t>
+          <t>Magnolia Inn</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2808 Hwy 90, Ste 1</t>
+          <t>704 Hwy 90</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5446,7 +5414,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>(228) 497-2424</t>
+          <t>(228) 522-0288</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -5454,7 +5422,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://www.yellowpages.com/gautier-ms/dentists</t>
+          <t>Hotel; no email found; Source: web search - https://allstays.com/hotels/32256.htm</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -5468,17 +5436,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Gautier Family Dental Group (Dr. Frank Winn, DDS)</t>
+          <t>Office/warehouse building - 3708 Hwy 90</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4551 Gautier Vancleave Rd, Ste A</t>
+          <t>3708 Hwy 90</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5491,21 +5459,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>(228) 497-6110</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>gautierfamilydentalgroup.com</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-frank-winn-d-d-s-gautier-ms</t>
+          <t>Freestanding office + 7,000 SF warehouse; for-lease listing; no email found; Source: web search - https://www.commercialsearch.com/commercial-property/us/ms/gautier/3708-highway-90-1/</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -5519,17 +5479,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Memorial Physician Clinics Gautier Walk-in Clinic</t>
+          <t>Two-story commercial complex - 2012 Hwy 90</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>726 US-90</t>
+          <t>2012 Hwy 90</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5548,7 +5508,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Hospital system; no email found; Source: web search - https://www.solvhealth.com/memorial-physician-clinics-gautier-walk-in-clinic-gautier-ms-AX84dA</t>
+          <t>For-sale listing, 1.69 acres; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/gautier/2012-highway-90/</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -5562,24 +5522,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Schroeder Real Estate Management</t>
+          <t>Dental office of Dr. Angela Baudean, DMD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Property Management</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>Medical Office</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>713 Hwy 90</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>39553</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>(228) 604-2455</t>
+          <t>(228) 201-3621</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -5587,7 +5555,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Manages Gautier rentals; office address not listed; no email found; Source: web search - https://www.apartments.com/2016-university-st-gautier-ms/55pydxn/</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-angela-baudean-d-m-d-gautier-ms</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -5601,24 +5569,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Shoreline Property Management / Shoreline Realty</t>
+          <t>Dental office of Dr. Jeffrey Knight, DDS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Property Management</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Medical Office</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3105 Shaw Dr</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>39553</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>(228) 875-3332</t>
+          <t>(228) 497-3111</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -5626,7 +5602,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Manages Exchange St duplexes in Gautier; office address not listed; no email found; Source: web search - https://www.zumper.com/apartment-buildings/p1472556/8100-8104-exchange-street-gautier-ms</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-jeffrey-knight-d-d-s-gautier-ms</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -5640,17 +5616,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ajo Y Oregano Latin Restaurant</t>
+          <t>Dental office of Dr. Michael Steward, DDS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>726 US-90, Ste F</t>
+          <t>4113 Gautier Vancleave Rd</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5663,13 +5639,21 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>(228) 497-1333</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>mikestewarddds.com</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-michael-steward-dds-gautier-ms</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -5683,17 +5667,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Antonio's Pizzeria</t>
+          <t>Gautier Family Dental Care</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2120 Ladnier Rd</t>
+          <t>2808 Hwy 90, Ste 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5706,13 +5690,17 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>(228) 497-2424</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
+          <t>Dental; no email found; Source: web search - https://www.yellowpages.com/gautier-ms/dentists</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -5726,17 +5714,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Burrito Zone</t>
+          <t>Gautier Family Dental Group (Dr. Frank Winn, DDS)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1115 US-90</t>
+          <t>4551 Gautier Vancleave Rd, Ste A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5749,13 +5737,21 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>(228) 497-6110</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>gautierfamilydentalgroup.com</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-frank-winn-d-d-s-gautier-ms</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -5769,17 +5765,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Crawfish House</t>
+          <t>Memorial Physician Clinics Gautier Walk-in Clinic</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3000 Oak St</t>
+          <t>726 US-90</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5798,7 +5794,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
+          <t>Hospital system; no email found; Source: web search - https://www.solvhealth.com/memorial-physician-clinics-gautier-walk-in-clinic-gautier-ms-AX84dA</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -5812,36 +5808,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Flower Patch</t>
+          <t>Schroeder Real Estate Management</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Restaurant</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>3204 Ladnier Rd, Ste 1</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>(228) 604-2455</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
+          <t>Manages Gautier rentals; office address not listed; no email found; Source: web search - https://www.apartments.com/2016-university-st-gautier-ms/55pydxn/</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -5855,36 +5847,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maty's Latin American Cuisine</t>
+          <t>Shoreline Property Management / Shoreline Realty</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Restaurant</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1449 Hwy 90</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>(228) 875-3332</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
+          <t>Manages Exchange St duplexes in Gautier; office address not listed; no email found; Source: web search - https://www.zumper.com/apartment-buildings/p1472556/8100-8104-exchange-street-gautier-ms</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -5898,7 +5886,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PawPaws Kountry Kitchen</t>
+          <t>Ajo Y Oregano Latin Restaurant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5908,7 +5896,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1600 Indian Point Rd</t>
+          <t>726 US-90, Ste F</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5941,7 +5929,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>The Tiki Bar and Grill</t>
+          <t>Antonio's Pizzeria</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5951,7 +5939,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>3212 Mary Walker Dr</t>
+          <t>2120 Ladnier Rd</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5984,17 +5972,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gautier Town Center</t>
+          <t>Burrito Zone</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2800 Hwy 90</t>
+          <t>1115 US-90</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6007,17 +5995,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>(504) 418-4189</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Shopping center; listing may be outdated; no email found; Source: web search - https://www.mallsinamerica.com/mississippi/gautier-town-center</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6031,17 +6015,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Harbor Freight Tools - Gautier</t>
+          <t>Crawfish House</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2029 Hwy 90</t>
+          <t>3000 Oak St</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6054,21 +6038,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>(228) 295-0411</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>harborfreight.com</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://go.harborfreight.com/store/harbor-freight-tools-in-gautier-ms-39553</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6082,17 +6058,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jackson Square Shopping Center</t>
+          <t>Flower Patch</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2525 Hwy 90</t>
+          <t>3204 Ladnier Rd, Ste 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6111,7 +6087,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Built 1981; brokers Coldwell Banker Alfonso Realty; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/gautier/2525-highway-90/</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6125,17 +6101,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Walgreens - Gautier</t>
+          <t>Maty's Latin American Cuisine</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2601 Hwy 90</t>
+          <t>1449 Hwy 90</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6148,21 +6124,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>(228) 497-8110</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>walgreens.com</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.walgreens.com/storelocator/atm/gautier-ms</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -6176,17 +6144,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Gautier Elementary</t>
+          <t>PawPaws Kountry Kitchen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>505 Magnolia Tree</t>
+          <t>1600 Indian Point Rd</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6199,17 +6167,13 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>(228) 522-8824</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -6223,17 +6187,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Gautier Middle School</t>
+          <t>The Tiki Bar and Grill</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1920 Graveline Rd</t>
+          <t>3212 Mary Walker Dr</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6241,18 +6205,18 @@
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>(228) 522-8806</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>39553</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Gautier/22348</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -6266,17 +6230,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1st Choice Storage</t>
+          <t>Gautier Town Center</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3301 US-90</t>
+          <t>2800 Hwy 90</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6289,13 +6253,17 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>(504) 418-4189</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>Shopping center; listing may be outdated; no email found; Source: web search - https://www.mallsinamerica.com/mississippi/gautier-town-center</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -6309,17 +6277,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Gautier Lock Storage</t>
+          <t>Harbor Freight Tools - Gautier</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2965 Old Spanish Trail</t>
+          <t>2029 Hwy 90</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6332,13 +6300,21 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>(228) 295-0411</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>harborfreight.com</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>National chain; no email found; Source: web search - https://go.harborfreight.com/store/harbor-freight-tools-in-gautier-ms-39553</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -6352,17 +6328,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Handy Lock Self Storage - Gautier</t>
+          <t>Jackson Square Shopping Center</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>4051 Gautier Vancleave Rd</t>
+          <t>2525 Hwy 90</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6381,7 +6357,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>Built 1981; brokers Coldwell Banker Alfonso Realty; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/gautier/2525-highway-90/</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -6395,17 +6371,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Homegrown Storage / Radiant Storage Gautier</t>
+          <t>Walgreens - Gautier</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3305 Townsend Rd</t>
+          <t>2601 Hwy 90</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6418,13 +6394,21 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>(228) 497-8110</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>walgreens.com</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Two names listed at same address; no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>National chain; no email found; Source: web search - https://www.walgreens.com/storelocator/atm/gautier-ms</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -6438,17 +6422,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Martin Bluff Storage</t>
+          <t>Gautier Elementary</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>6220 Martin Bluff Rd</t>
+          <t>505 Magnolia Tree</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6461,13 +6445,17 @@
           <t>39553</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>(228) 522-8824</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -6481,17 +6469,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Singing River Storage</t>
+          <t>Gautier Middle School</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>3719 Beasley Rd</t>
+          <t>1920 Graveline Rd</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6499,18 +6487,18 @@
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>(228) 522-8806</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -6524,27 +6512,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A &amp; B Tire</t>
+          <t>1st Choice Storage</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>6800 Grierson St</t>
+          <t>3301 US-90</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6553,7 +6541,7 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
+          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -6567,27 +6555,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Affordable Automotive Care</t>
+          <t>Gautier Lock Storage</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>7621 Elder Ferry Rd</t>
+          <t>2965 Old Spanish Trail</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6596,7 +6584,7 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
+          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -6610,27 +6598,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Donovan's Auto Repair</t>
+          <t>Handy Lock Self Storage - Gautier</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>6630 Grierson St</t>
+          <t>4051 Gautier Vancleave Rd</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -6639,7 +6627,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
+          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -6653,27 +6641,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Estabrook Toyota</t>
+          <t>Homegrown Storage / Radiant Storage Gautier</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>6521 Hwy 63</t>
+          <t>3305 Townsend Rd</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6682,7 +6670,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Dealership + service; no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
+          <t>Two names listed at same address; no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -6696,27 +6684,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Johnson Tire Service, LLC</t>
+          <t>Martin Bluff Storage</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>5906 Hwy 63</t>
+          <t>6220 Martin Bluff Rd</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -6725,7 +6713,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Misfit Automotive Diesel and Marine also listed at this address; no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
+          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -6739,40 +6727,36 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Abundance of Blessings Church</t>
+          <t>Singing River Storage</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Storage Facility</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>4031 Washington Blvd</t>
+          <t>3719 Beasley Rd</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>39563</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>(228) 217-8259</t>
-        </is>
-      </c>
+          <t>39553</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Calling All Christians Church also listed at this address; no email found; Source: web search - https://feedam.org/resource/175170</t>
+          <t>no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -6786,17 +6770,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Church of St. Joseph (Catholic)</t>
+          <t>A &amp; B Tire</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1st St &amp; Dr. Martin Luther King Dr</t>
+          <t>6800 Grierson St</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6806,20 +6790,16 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>39562</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>(228) 475-0777</t>
-        </is>
-      </c>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30122</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -6833,17 +6813,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Safe Harbor United Methodist</t>
+          <t>Affordable Automotive Care</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>12000 Hwy 63</t>
+          <t>7621 Elder Ferry Rd</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6853,7 +6833,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -6862,7 +6842,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://churcheslist.com/?p=15911</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -6876,17 +6856,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Second Missionary Baptist Church</t>
+          <t>Donovan's Auto Repair</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>3913 Macphelah Rd</t>
+          <t>6630 Grierson St</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6899,17 +6879,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>(228) 235-5418</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.gmbsc.org/church-directory/second-missionary-baptist-church</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -6923,17 +6899,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Trinity Bible Church Independent Methodist</t>
+          <t>Estabrook Toyota</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>7313 Elder Ferry Rd</t>
+          <t>6521 Hwy 63</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6952,7 +6928,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://churcheslist.com/?p=15906</t>
+          <t>Dealership + service; no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -6966,17 +6942,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Unity Primitive Baptist Church</t>
+          <t>Johnson Tire Service, LLC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>11500 MS-63</t>
+          <t>5906 Hwy 63</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6995,7 +6971,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Listed phone was invalid - not recorded; no email found; Source: web search - https://primitivebaptistsermons.org/modern/church-details.php?id=239</t>
+          <t>Misfit Automotive Diesel and Marine also listed at this address; no email found; Source: web search - https://www.iexitapp.com/exits/Mississippi/I-10/West/647/Auto%20Repair/2465</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -7009,17 +6985,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Best Western Flagship Inn</t>
+          <t>Abundance of Blessings Church</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>4830 Amoco Dr</t>
+          <t>4031 Washington Blvd</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7034,7 +7010,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>(228) 475-5000</t>
+          <t>(228) 217-8259</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -7042,7 +7018,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
+          <t>Calling All Christians Church also listed at this address; no email found; Source: web search - https://feedam.org/resource/175170</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -7056,36 +7032,40 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Comfort Inn &amp; Suites Moss Point Pascagoula</t>
+          <t>Church of St. Joseph (Catholic)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>1st St &amp; Dr. Martin Luther King Dr</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>39562</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>(228) 474-3600</t>
+          <t>(228) 475-0777</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>choicehotels.com</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Hotel; off I-10; no email found; Source: web search - https://www.choicehotels.com/hotel/ms418</t>
+          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30122</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -7099,17 +7079,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Days Inn by Wyndham Moss Point</t>
+          <t>Safe Harbor United Methodist</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>6700 Hwy 63 S</t>
+          <t>12000 Hwy 63</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7119,20 +7099,16 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>39563</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>(228) 475-0077</t>
-        </is>
-      </c>
+          <t>39562</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
+          <t>no email found; Source: web search - https://churcheslist.com/?p=15911</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -7146,17 +7122,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Econo Lodge Moss Point - Pascagoula</t>
+          <t>Second Missionary Baptist Church</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>6623 Hwy 63</t>
+          <t>3913 Macphelah Rd</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7169,13 +7145,17 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>(228) 235-5418</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://www.hotelplanner.com/Hotels/15017-in-Pascagoula-MS</t>
+          <t>no email found; Source: web search - https://www.gmbsc.org/church-directory/second-missionary-baptist-church</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -7189,17 +7169,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Hampton Inn Moss Point Pascagoula</t>
+          <t>Trinity Bible Church Independent Methodist</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>6730 Hwy 63 N</t>
+          <t>7313 Elder Ferry Rd</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7212,17 +7192,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>(228) 246-0777</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
+          <t>no email found; Source: web search - https://churcheslist.com/?p=15906</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -7236,17 +7212,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Holiday Inn Express Moss Point</t>
+          <t>Unity Primitive Baptist Church</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>4800 Amoco Dr</t>
+          <t>11500 MS-63</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7259,17 +7235,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>(228) 474-2100</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://www.travelagewest.com/Hotels/Moss-Point-MS/Holiday-Inn-Express-Pascagoula-p52868033</t>
+          <t>Listed phone was invalid - not recorded; no email found; Source: web search - https://primitivebaptistsermons.org/modern/church-details.php?id=239</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -7283,7 +7255,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Office building - 3630 Main St</t>
+          <t>Best Western Flagship Inn</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7293,7 +7265,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>3630 Main St</t>
+          <t>4830 Amoco Dr</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7301,14 +7273,22 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>(228) 475-5000</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>1,854 SF office, for-sale listing - verify; no email found; Source: web search - https://www.crexi.com/properties/MS/Jackson_County/Traditional_Office</t>
+          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -7322,7 +7302,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Retail building - 7500 Hwy 613</t>
+          <t>Comfort Inn &amp; Suites Moss Point Pascagoula</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7330,24 +7310,28 @@
           <t>Commercial Building</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>7500 Hwy 613</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>Moss Point</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>(228) 474-3600</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>choicehotels.com</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Freestanding building for lease near I-10; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/moss-point/7500-highway-613/</t>
+          <t>Hotel; off I-10; no email found; Source: web search - https://www.choicehotels.com/hotel/ms418</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -7361,17 +7345,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Eriks Moss Point</t>
+          <t>Days Inn by Wyndham Moss Point</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>6407 Hwy 90</t>
+          <t>6700 Hwy 63 S</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7384,13 +7368,17 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>(228) 475-0077</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://cn.panjiva.com/Eriks-Moss-Point/61469509</t>
+          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -7404,17 +7392,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Industrial building - 4020 Jefferson Ave</t>
+          <t>Econo Lodge Moss Point - Pascagoula</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>4020 Jefferson Ave</t>
+          <t>6623 Hwy 63</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7422,14 +7410,18 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2,800 SF on 1.76 acres; for lease; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/moss-point/2-800-sf-industrial-facility-on-1-76-acres-1/</t>
+          <t>Hotel; no email found; Source: web search - https://www.hotelplanner.com/Hotels/15017-in-Pascagoula-MS</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -7443,17 +7435,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Lee High Performance Boats &amp; Marine</t>
+          <t>Hampton Inn Moss Point Pascagoula</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>7616 Browns Rd</t>
+          <t>6730 Hwy 63 N</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7461,10 +7453,14 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>(228) 219-9375</t>
+          <t>(228) 246-0777</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -7472,7 +7468,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://uscgboating.org/content/manufacturers-identification-detail.php?id=7269</t>
+          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -7486,17 +7482,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Mississippi Export Railroad</t>
+          <t>Holiday Inn Express Moss Point</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>4519 McInnis Ave</t>
+          <t>4800 Amoco Dr</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7511,19 +7507,15 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>(228) 474-0710</t>
+          <t>(228) 474-2100</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>mserr.com</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://mserr.com/services/industrial-sites/moss-point/</t>
+          <t>Hotel; no email found; Source: web search - https://www.travelagewest.com/Hotels/Moss-Point-MS/Holiday-Inn-Express-Pascagoula-p52868033</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -7537,17 +7529,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Riverside Dental (Dr. Wayne Adkison, DMD)</t>
+          <t>Office building - 3630 Main St</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>4400 McInnis Ave</t>
+          <t>3630 Main St</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7555,26 +7547,14 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>39563</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>(228) 475-0005</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>riversidedocs.com</t>
-        </is>
-      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-wayne-adkison-dmd-moss-point-ms</t>
+          <t>1,854 SF office, for-sale listing - verify; no email found; Source: web search - https://www.crexi.com/properties/MS/Jackson_County/Traditional_Office</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -7588,17 +7568,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Accu-Fab &amp; Construction, Inc.</t>
+          <t>Retail building - 7500 Hwy 613</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Metal Building</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5313 Mirror Lake Rd</t>
+          <t>7500 Hwy 613</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7606,22 +7586,14 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>39562</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>(228) 475-0082</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>40,000 sq ft fabrication facility; no email found; Source: web search - https://www.globalspec.com/local/3262/C_US/MS/Moss Point</t>
+          <t>Freestanding building for lease near I-10; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/moss-point/7500-highway-613/</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -7635,17 +7607,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Burger King - Moss Point</t>
+          <t>Eriks Moss Point</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>6527 Hwy 63</t>
+          <t>6407 Hwy 90</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7664,7 +7636,7 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.ubereats.com/dish/moss-point-ms/meat-lovers-pizza</t>
+          <t>no email found; Source: web search - https://cn.panjiva.com/Eriks-Moss-Point/61469509</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -7678,17 +7650,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cracker Barrel - Moss Point</t>
+          <t>Industrial building - 4020 Jefferson Ave</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>6805 Hwy 63 N</t>
+          <t>4020 Jefferson Ave</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7696,18 +7668,14 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>39563</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.ubereats.com/pgc2up/dish/moss-point-ms/hash-brown</t>
+          <t>2,800 SF on 1.76 acres; for lease; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/moss-point/2-800-sf-industrial-facility-on-1-76-acres-1/</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -7721,17 +7689,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Good Bros Seafood</t>
+          <t>Lee High Performance Boats &amp; Marine</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>3831 Main St</t>
+          <t>7616 Browns Rd</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7739,18 +7707,18 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>39563</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>(228) 219-9375</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
+          <t>no email found; Source: web search - https://uscgboating.org/content/manufacturers-identification-detail.php?id=7269</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -7764,17 +7732,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Hacienda San Miguel: House of Tequila</t>
+          <t>Mississippi Export Railroad</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>4833 Amoco Dr</t>
+          <t>4519 McInnis Ave</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7787,13 +7755,21 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>(228) 474-0710</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>mserr.com</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
+          <t>no email found; Source: web search - https://mserr.com/services/industrial-sites/moss-point/</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -7807,17 +7783,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Lakeview Catfish Restaurant</t>
+          <t>Riverside Dental (Dr. Wayne Adkison, DMD)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>9701 US-90</t>
+          <t>4400 McInnis Ave</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7827,20 +7803,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>(228) 475-3552</t>
+          <t>(228) 475-0005</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>riversidedocs.com</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://tableagent.com/gulfport-biloxi/lakeview-catfish-restaurant/</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-wayne-adkison-dmd-moss-point-ms</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -7854,17 +7834,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Los Arcos</t>
+          <t>Accu-Fab &amp; Construction, Inc.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Metal Building</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>3512 Main St</t>
+          <t>5313 Mirror Lake Rd</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7874,16 +7854,20 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>39563</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
+          <t>39562</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>(228) 475-0082</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
+          <t>40,000 sq ft fabrication facility; no email found; Source: web search - https://www.globalspec.com/local/3262/C_US/MS/Moss Point</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -7897,7 +7881,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sonic Drive-In - Moss Point</t>
+          <t>Burger King - Moss Point</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7907,7 +7891,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>4725 Main St</t>
+          <t>6527 Hwy 63</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7926,7 +7910,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
+          <t>National chain; no email found; Source: web search - https://www.ubereats.com/dish/moss-point-ms/meat-lovers-pizza</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -7940,7 +7924,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Wendy's - Moss Point</t>
+          <t>Cracker Barrel - Moss Point</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7950,7 +7934,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>6533 Hwy 63</t>
+          <t>6805 Hwy 63 N</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7969,7 +7953,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.ubereats.com/dish/moss-point-ms/meat-lovers-pizza</t>
+          <t>National chain; no email found; Source: web search - https://www.ubereats.com/pgc2up/dish/moss-point-ms/hash-brown</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -7983,17 +7967,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Pilot Travel Center #586</t>
+          <t>Good Bros Seafood</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>6705 Hwy 63</t>
+          <t>3831 Main St</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8012,7 +7996,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>From fuel-tank registry - may be outdated; large canopy/store roof; no email found; Source: web search - https://ustmap.com/mississippi/moss-point</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -8026,17 +8010,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Magnolia Middle School</t>
+          <t>Hacienda San Miguel: House of Tequila</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>4630 Magnolia St</t>
+          <t>4833 Amoco Dr</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8049,17 +8033,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>(228) 475-1832</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Moss Point SD; no email found; Source: web search - https://feedam.org/resource/310531</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -8073,17 +8053,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Moss Point Alternative School</t>
+          <t>Lakeview Catfish Restaurant</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>4913 Weems St</t>
+          <t>9701 US-90</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8093,12 +8073,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>(228) 475-3543</t>
+          <t>(228) 475-3552</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -8106,7 +8086,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Same campus address as Moss Point High; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
+          <t>no email found; Source: web search - https://tableagent.com/gulfport-biloxi/lakeview-catfish-restaurant/</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -8120,17 +8100,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Moss Point Escatawpa Upper Elementary</t>
+          <t>Los Arcos</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>4208 Jamestown Rd</t>
+          <t>3512 Main St</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8143,17 +8123,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>(228) 474-3300</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Moss Point SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
+          <t>no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -8167,17 +8143,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Moss Point High School</t>
+          <t>Sonic Drive-In - Moss Point</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>4913 Weems St</t>
+          <t>4725 Main St</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8190,17 +8166,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>(228) 475-5721</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Another listing gives (228) 475-5058; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+          <t>National chain; no email found; Source: web search - https://www.iexitapp.com/guide/Mississippi/23/Moss%20Point/22447</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -8214,17 +8186,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Moss Point School District Office</t>
+          <t>Wendy's - Moss Point</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>4924 Church St</t>
+          <t>6533 Hwy 63</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8237,17 +8209,13 @@
           <t>39563</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>(228) 475-4558</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>District facilities dept handles all campuses; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+          <t>National chain; no email found; Source: web search - https://www.ubereats.com/dish/moss-point-ms/meat-lovers-pizza</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -8261,17 +8229,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Moss Point Self Storage</t>
+          <t>Pilot Travel Center #586</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2305 Mangrove Rd</t>
+          <t>6705 Hwy 63</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8281,7 +8249,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -8290,7 +8258,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Name not given in listing; no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+          <t>From fuel-tank registry - may be outdated; large canopy/store roof; no email found; Source: web search - https://ustmap.com/mississippi/moss-point</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -8304,17 +8272,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Former Frito-Lay distribution warehouse</t>
+          <t>Magnolia Middle School</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>10816 Hwy 63</t>
+          <t>4630 Magnolia St</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8322,14 +8290,22 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>(228) 475-1832</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>~89,734 SF; vacant Oct 1, 2026 - for lease; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/moss-point/10816-highway-63/</t>
+          <t>Moss Point SD; no email found; Source: web search - https://feedam.org/resource/310531</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -8343,17 +8319,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Warehouse - 6124 Shortcut Rd</t>
+          <t>Moss Point Alternative School</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>6124 Shortcut Rd</t>
+          <t>4913 Weems St</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8361,14 +8337,22 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>(228) 475-3543</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>7,200 SF warehouse + office; vacant, for sale/lease; no email found; Source: web search - https://www.crexi.com/properties/1883301/mississippi-7200-sf-warehouse-for-sale-or-lease</t>
+          <t>Same campus address as Moss Point High; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -8379,8 +8363,270 @@
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Moss Point Escatawpa Upper Elementary</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4208 Jamestown Rd</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>(228) 474-3300</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Moss Point SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Moss Point High School</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>4913 Weems St</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>(228) 475-5721</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Another listing gives (228) 475-5058; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Moss Point School District Office</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>4924 Church St</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>(228) 475-4558</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>District facilities dept handles all campuses; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Moss Point Self Storage</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Storage Facility</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2305 Mangrove Rd</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>39562</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Name not given in listing; no email found; Source: web search - https://www.storagecafe.com/self-storage/us/ms/moss-point/</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Former Frito-Lay distribution warehouse</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>10816 Hwy 63</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>~89,734 SF; vacant Oct 1, 2026 - for lease; no email found; Source: web search - https://www.commercialcafe.com/commercial-property/us/ms/moss-point/10816-highway-63/</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Warehouse - 6124 Shortcut Rd</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>6124 Shortcut Rd</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>7,200 SF warehouse + office; vacant, for sale/lease; no email found; Source: web search - https://www.crexi.com/properties/1883301/mississippi-7200-sf-warehouse-for-sale-or-lease</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M179"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8391,10 +8637,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -9685,17 +9931,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Alfonso Property Management / Coldwell Banker Commercial Alfonso Realty</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Property Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3400 Chicot St</t>
+          <t>934 Jackson Ave</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -9705,20 +9951,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(228) 762-8660</t>
+          <t>(228) 818-5788</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>alfonsopm.com</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
+          <t>Residential + commercial property management and commercial leasing; brokers for Jackson Square (Gautier); no email found; Source: web search - https://alfonsopmjacksoncounty.property-genie.com/</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -9732,17 +9982,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NAPA Auto Parts</t>
+          <t>Dantzler Management</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Property Management</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4009 14th St</t>
+          <t>3207 Frederic St</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -9750,14 +10000,10 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>39567</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(228) 762-1344</t>
+          <t>(228) 762-4611</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -9765,7 +10011,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
+          <t>In business 55 years per Yellow Pages; no email found; Source: web search - https://www.yellowpages.com/pascagoula-ms/property-management</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -9779,17 +10025,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Arlington Elementary</t>
+          <t>Dronet Realty &amp; Property Management</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Property Management</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3511 Arlington St</t>
+          <t>1741 Jackson Ave</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9799,12 +10045,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(228) 938-6552</t>
+          <t>(228) 447-3727</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -9812,7 +10058,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
+          <t>Residential, commercial and land management; no email found; Source: web search - https://www.facebook.com/dronetrealty/</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -9826,17 +10072,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jackson Elementary</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3203 Lanier St</t>
+          <t>3400 Chicot St</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -9844,10 +10090,14 @@
           <t>Pascagoula</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>39581</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>(228) 938-6554</t>
+          <t>(228) 762-8660</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -9855,7 +10105,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Closing after 2025-26 school year; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39567/search.aspx</t>
+          <t>National chain; no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -9869,17 +10119,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Warehouse - 2205 Petit Bois St</t>
+          <t>NAPA Auto Parts</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2205 Petit Bois St</t>
+          <t>4009 14th St</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9889,12 +10139,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>(228) 365-8763</t>
+          <t>(228) 762-1344</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -9902,7 +10152,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>For sale; phone is listing contact; no email found; Source: web search - https://www.showcase.com/2205-petit-bois-st-pascagoula-ms-39581/35200689/</t>
+          <t>no email found; Source: web search - https://www.napaonline.com/en/auto-parts-stores-near-me/ms/pascagoula</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9916,32 +10166,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ante Bellum Manor (condos)</t>
+          <t>Arlington Elementary</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apartment Complex</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5080 Gautier Vancleave Rd</t>
+          <t>3511 Arlington St</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(228) 447-3727</t>
+          <t>(228) 938-6552</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -9949,7 +10199,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Phone is from a unit rental listing; no email found; Source: web search - https://www.apartments.com/5080-gautier-vancleave-rd-gautier-ms/58b795p/</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03480/search.aspx</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9963,32 +10213,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Firestone Complete Auto Care - Gautier</t>
+          <t>Jackson Elementary</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Auto Shop / Dealership</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3299 Old Spanish Trail</t>
+          <t>3203 Lanier St</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Gautier</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
+          <t>Pascagoula</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(228) 497-7014</t>
+          <t>(228) 938-6554</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -9996,7 +10242,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.kbb.com/service-centers/gautier-ms</t>
+          <t>Closing after 2025-26 school year; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39567/search.aspx</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -10010,32 +10256,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Church of St. Mary (Catholic)</t>
+          <t>Warehouse - 2205 Petit Bois St</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>809 De La Pointe Dr</t>
+          <t>2205 Petit Bois St</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gautier</t>
+          <t>Pascagoula</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>(228) 497-2364</t>
+          <t>(228) 365-8763</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -10043,7 +10289,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30128</t>
+          <t>For sale; phone is listing contact; no email found; Source: web search - https://www.showcase.com/2205-petit-bois-st-pascagoula-ms-39581/35200689/</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10057,17 +10303,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gautier First United Methodist Church</t>
+          <t>Ante Bellum Manor (condos)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Apartment Complex</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2717 Hwy 90</t>
+          <t>5080 Gautier Vancleave Rd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10082,7 +10328,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>(228) 497-1698</t>
+          <t>(228) 447-3727</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -10090,7 +10336,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Phone from church directory search result - verify; no email found; Source: web search - https://feedam.org/resource/172621</t>
+          <t>Phone is Dronet Realty &amp; Property Management (listing agent); no email found; Source: web search - https://www.apartments.com/5080-gautier-vancleave-rd-gautier-ms/58b795p/</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10104,17 +10350,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Magnolia Inn</t>
+          <t>Firestone Complete Auto Care - Gautier</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Auto Shop / Dealership</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>704 Hwy 90</t>
+          <t>3299 Old Spanish Trail</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -10129,7 +10375,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>(228) 522-0288</t>
+          <t>(228) 497-7014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -10137,7 +10383,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://allstays.com/hotels/32256.htm</t>
+          <t>National chain; no email found; Source: web search - https://www.kbb.com/service-centers/gautier-ms</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10151,17 +10397,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dental office of Dr. Angela Baudean, DMD</t>
+          <t>Church of St. Mary (Catholic)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>713 Hwy 90</t>
+          <t>809 De La Pointe Dr</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10176,7 +10422,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>(228) 201-3621</t>
+          <t>(228) 497-2364</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -10184,7 +10430,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-angela-baudean-d-m-d-gautier-ms</t>
+          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30128</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -10198,17 +10444,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dental office of Dr. Jeffrey Knight, DDS</t>
+          <t>Gautier First United Methodist Church</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3105 Shaw Dr</t>
+          <t>2717 Hwy 90</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -10223,7 +10469,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(228) 497-3111</t>
+          <t>(228) 497-1698</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -10231,7 +10477,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-jeffrey-knight-d-d-s-gautier-ms</t>
+          <t>Phone from church directory search result - verify; no email found; Source: web search - https://feedam.org/resource/172621</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -10245,17 +10491,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dental office of Dr. Michael Steward, DDS</t>
+          <t>Magnolia Inn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4113 Gautier Vancleave Rd</t>
+          <t>704 Hwy 90</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -10270,19 +10516,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>(228) 497-1333</t>
+          <t>(228) 522-0288</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>mikestewarddds.com</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-michael-steward-dds-gautier-ms</t>
+          <t>Hotel; no email found; Source: web search - https://allstays.com/hotels/32256.htm</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -10296,7 +10538,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gautier Family Dental Care</t>
+          <t>Dental office of Dr. Angela Baudean, DMD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10306,7 +10548,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2808 Hwy 90, Ste 1</t>
+          <t>713 Hwy 90</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -10321,7 +10563,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>(228) 497-2424</t>
+          <t>(228) 201-3621</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -10329,7 +10571,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://www.yellowpages.com/gautier-ms/dentists</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-angela-baudean-d-m-d-gautier-ms</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -10343,7 +10585,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gautier Family Dental Group (Dr. Frank Winn, DDS)</t>
+          <t>Dental office of Dr. Jeffrey Knight, DDS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10353,7 +10595,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4551 Gautier Vancleave Rd, Ste A</t>
+          <t>3105 Shaw Dr</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -10368,19 +10610,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>(228) 497-6110</t>
+          <t>(228) 497-3111</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>gautierfamilydentalgroup.com</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-frank-winn-d-d-s-gautier-ms</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-jeffrey-knight-d-d-s-gautier-ms</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -10394,32 +10632,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Schroeder Real Estate Management</t>
+          <t>Dental office of Dr. Michael Steward, DDS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Property Management</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Medical Office</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4113 Gautier Vancleave Rd</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>39553</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>(228) 604-2455</t>
+          <t>(228) 497-1333</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>mikestewarddds.com</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Manages Gautier rentals; office address not listed; no email found; Source: web search - https://www.apartments.com/2016-university-st-gautier-ms/55pydxn/</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-michael-steward-dds-gautier-ms</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -10433,24 +10683,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shoreline Property Management / Shoreline Realty</t>
+          <t>Gautier Family Dental Care</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Property Management</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Medical Office</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2808 Hwy 90, Ste 1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>39553</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>(228) 875-3332</t>
+          <t>(228) 497-2424</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -10458,7 +10716,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Manages Exchange St duplexes in Gautier; office address not listed; no email found; Source: web search - https://www.zumper.com/apartment-buildings/p1472556/8100-8104-exchange-street-gautier-ms</t>
+          <t>Dental; no email found; Source: web search - https://www.yellowpages.com/gautier-ms/dentists</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -10472,17 +10730,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gautier Town Center</t>
+          <t>Gautier Family Dental Group (Dr. Frank Winn, DDS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2800 Hwy 90</t>
+          <t>4551 Gautier Vancleave Rd, Ste A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -10497,15 +10755,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(504) 418-4189</t>
+          <t>(228) 497-6110</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>gautierfamilydentalgroup.com</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Shopping center; listing may be outdated; no email found; Source: web search - https://www.mallsinamerica.com/mississippi/gautier-town-center</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-frank-winn-d-d-s-gautier-ms</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -10519,44 +10781,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Harbor Freight Tools - Gautier</t>
+          <t>Schroeder Real Estate Management</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2029 Hwy 90</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(228) 295-0411</t>
+          <t>(228) 604-2455</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>harborfreight.com</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://go.harborfreight.com/store/harbor-freight-tools-in-gautier-ms-39553</t>
+          <t>Manages Gautier rentals; office address not listed; no email found; Source: web search - https://www.apartments.com/2016-university-st-gautier-ms/55pydxn/</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -10570,44 +10820,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Walgreens - Gautier</t>
+          <t>Shoreline Property Management / Shoreline Realty</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Retail / Strip Center</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2601 Hwy 90</t>
-        </is>
-      </c>
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>39553</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>(228) 497-8110</t>
+          <t>(228) 875-3332</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>walgreens.com</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>National chain; no email found; Source: web search - https://www.walgreens.com/storelocator/atm/gautier-ms</t>
+          <t>Manages Exchange St duplexes in Gautier; office address not listed; no email found; Source: web search - https://www.zumper.com/apartment-buildings/p1472556/8100-8104-exchange-street-gautier-ms</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -10621,17 +10859,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gautier Elementary</t>
+          <t>Gautier Town Center</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>505 Magnolia Tree</t>
+          <t>2800 Hwy 90</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10646,7 +10884,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(228) 522-8824</t>
+          <t>(504) 418-4189</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -10654,7 +10892,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
+          <t>Shopping center; listing may be outdated; no email found; Source: web search - https://www.mallsinamerica.com/mississippi/gautier-town-center</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -10668,17 +10906,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gautier Middle School</t>
+          <t>Harbor Freight Tools - Gautier</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1920 Graveline Rd</t>
+          <t>2029 Hwy 90</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10686,18 +10924,26 @@
           <t>Gautier</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>39553</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>(228) 522-8806</t>
+          <t>(228) 295-0411</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>harborfreight.com</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
+          <t>National chain; no email found; Source: web search - https://go.harborfreight.com/store/harbor-freight-tools-in-gautier-ms-39553</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -10711,40 +10957,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Abundance of Blessings Church</t>
+          <t>Walgreens - Gautier</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Retail / Strip Center</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4031 Washington Blvd</t>
+          <t>2601 Hwy 90</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>(228) 217-8259</t>
+          <t>(228) 497-8110</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>walgreens.com</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Calling All Christians Church also listed at this address; no email found; Source: web search - https://feedam.org/resource/175170</t>
+          <t>National chain; no email found; Source: web search - https://www.walgreens.com/storelocator/atm/gautier-ms</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -10758,32 +11008,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Church of St. Joseph (Catholic)</t>
+          <t>Gautier Elementary</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1st St &amp; Dr. Martin Luther King Dr</t>
+          <t>505 Magnolia Tree</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Moss Point</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>(228) 475-0777</t>
+          <t>(228) 522-8824</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -10791,7 +11041,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30122</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -10805,32 +11055,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Second Missionary Baptist Church</t>
+          <t>Gautier Middle School</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3913 Macphelah Rd</t>
+          <t>1920 Graveline Rd</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Moss Point</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>39563</t>
-        </is>
-      </c>
+          <t>Gautier</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(228) 235-5418</t>
+          <t>(228) 522-8806</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -10838,7 +11084,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://www.gmbsc.org/church-directory/second-missionary-baptist-church</t>
+          <t>Pascagoula-Gautier SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/city/Gautier/search.aspx</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -10852,17 +11098,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Best Western Flagship Inn</t>
+          <t>Abundance of Blessings Church</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4830 Amoco Dr</t>
+          <t>4031 Washington Blvd</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10877,7 +11123,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>(228) 475-5000</t>
+          <t>(228) 217-8259</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -10885,7 +11131,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
+          <t>Calling All Christians Church also listed at this address; no email found; Source: web search - https://feedam.org/resource/175170</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -10899,36 +11145,40 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Comfort Inn &amp; Suites Moss Point Pascagoula</t>
+          <t>Church of St. Joseph (Catholic)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1st St &amp; Dr. Martin Luther King Dr</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>39562</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(228) 474-3600</t>
+          <t>(228) 475-0777</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>choicehotels.com</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Hotel; off I-10; no email found; Source: web search - https://www.choicehotels.com/hotel/ms418</t>
+          <t>no email found; Source: web search - https://gcatholic.org/churches/usa-05/30122</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -10942,17 +11192,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Days Inn by Wyndham Moss Point</t>
+          <t>Second Missionary Baptist Church</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>6700 Hwy 63 S</t>
+          <t>3913 Macphelah Rd</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -10967,7 +11217,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>(228) 475-0077</t>
+          <t>(228) 235-5418</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -10975,7 +11225,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
+          <t>no email found; Source: web search - https://www.gmbsc.org/church-directory/second-missionary-baptist-church</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -10989,7 +11239,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hampton Inn Moss Point Pascagoula</t>
+          <t>Best Western Flagship Inn</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10999,7 +11249,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6730 Hwy 63 N</t>
+          <t>4830 Amoco Dr</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11014,7 +11264,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(228) 246-0777</t>
+          <t>(228) 475-5000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -11036,7 +11286,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Holiday Inn Express Moss Point</t>
+          <t>Comfort Inn &amp; Suites Moss Point Pascagoula</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11044,32 +11294,28 @@
           <t>Commercial Building</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>4800 Amoco Dr</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>39563</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>(228) 474-2100</t>
+          <t>(228) 474-3600</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>choicehotels.com</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Hotel; no email found; Source: web search - https://www.travelagewest.com/Hotels/Moss-Point-MS/Holiday-Inn-Express-Pascagoula-p52868033</t>
+          <t>Hotel; off I-10; no email found; Source: web search - https://www.choicehotels.com/hotel/ms418</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -11083,17 +11329,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lee High Performance Boats &amp; Marine</t>
+          <t>Days Inn by Wyndham Moss Point</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7616 Browns Rd</t>
+          <t>6700 Hwy 63 S</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11101,10 +11347,14 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>(228) 219-9375</t>
+          <t>(228) 475-0077</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -11112,7 +11362,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://uscgboating.org/content/manufacturers-identification-detail.php?id=7269</t>
+          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -11126,17 +11376,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mississippi Export Railroad</t>
+          <t>Hampton Inn Moss Point Pascagoula</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>4519 McInnis Ave</t>
+          <t>6730 Hwy 63 N</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11151,19 +11401,15 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>(228) 474-0710</t>
+          <t>(228) 246-0777</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>mserr.com</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://mserr.com/services/industrial-sites/moss-point/</t>
+          <t>Hotel; no email found; Source: web search - https://pascagoula.chevron.com/contact</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -11177,17 +11423,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Riverside Dental (Dr. Wayne Adkison, DMD)</t>
+          <t>Holiday Inn Express Moss Point</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Commercial Building</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>4400 McInnis Ave</t>
+          <t>4800 Amoco Dr</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -11202,19 +11448,15 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>(228) 475-0005</t>
+          <t>(228) 474-2100</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>riversidedocs.com</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-wayne-adkison-dmd-moss-point-ms</t>
+          <t>Hotel; no email found; Source: web search - https://www.travelagewest.com/Hotels/Moss-Point-MS/Holiday-Inn-Express-Pascagoula-p52868033</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -11228,17 +11470,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Accu-Fab &amp; Construction, Inc.</t>
+          <t>Lee High Performance Boats &amp; Marine</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Metal Building</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5313 Mirror Lake Rd</t>
+          <t>7616 Browns Rd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11246,14 +11488,10 @@
           <t>Moss Point</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>39562</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>(228) 475-0082</t>
+          <t>(228) 219-9375</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -11261,7 +11499,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>40,000 sq ft fabrication facility; no email found; Source: web search - https://www.globalspec.com/local/3262/C_US/MS/Moss Point</t>
+          <t>no email found; Source: web search - https://uscgboating.org/content/manufacturers-identification-detail.php?id=7269</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -11275,17 +11513,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lakeview Catfish Restaurant</t>
+          <t>Mississippi Export Railroad</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9701 US-90</t>
+          <t>4519 McInnis Ave</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -11295,20 +11533,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>39563</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>(228) 475-3552</t>
+          <t>(228) 474-0710</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>mserr.com</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>no email found; Source: web search - https://tableagent.com/gulfport-biloxi/lakeview-catfish-restaurant/</t>
+          <t>no email found; Source: web search - https://mserr.com/services/industrial-sites/moss-point/</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -11322,17 +11564,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Magnolia Middle School</t>
+          <t>Riverside Dental (Dr. Wayne Adkison, DMD)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Medical Office</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>4630 Magnolia St</t>
+          <t>4400 McInnis Ave</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -11347,15 +11589,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>(228) 475-1832</t>
+          <t>(228) 475-0005</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>riversidedocs.com</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Moss Point SD; no email found; Source: web search - https://feedam.org/resource/310531</t>
+          <t>Dental; no email found; Source: web search - https://local.newpatientsinc.com/dental/dr-wayne-adkison-dmd-moss-point-ms</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -11369,17 +11615,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Moss Point Alternative School</t>
+          <t>Accu-Fab &amp; Construction, Inc.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Metal Building</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>4913 Weems St</t>
+          <t>5313 Mirror Lake Rd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -11389,12 +11635,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>(228) 475-3543</t>
+          <t>(228) 475-0082</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -11402,7 +11648,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Same campus address as Moss Point High; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
+          <t>40,000 sq ft fabrication facility; no email found; Source: web search - https://www.globalspec.com/local/3262/C_US/MS/Moss Point</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -11416,17 +11662,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Moss Point Escatawpa Upper Elementary</t>
+          <t>Lakeview Catfish Restaurant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4208 Jamestown Rd</t>
+          <t>9701 US-90</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -11436,12 +11682,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>(228) 474-3300</t>
+          <t>(228) 475-3552</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -11449,7 +11695,7 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Moss Point SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
+          <t>no email found; Source: web search - https://tableagent.com/gulfport-biloxi/lakeview-catfish-restaurant/</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -11463,7 +11709,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Moss Point High School</t>
+          <t>Magnolia Middle School</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11473,7 +11719,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4913 Weems St</t>
+          <t>4630 Magnolia St</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11488,7 +11734,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>(228) 475-5721</t>
+          <t>(228) 475-1832</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -11496,7 +11742,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Another listing gives (228) 475-5058; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+          <t>Moss Point SD; no email found; Source: web search - https://feedam.org/resource/310531</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -11510,7 +11756,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Moss Point School District Office</t>
+          <t>Moss Point Alternative School</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11520,7 +11766,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4924 Church St</t>
+          <t>4913 Weems St</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11535,7 +11781,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>(228) 475-4558</t>
+          <t>(228) 475-3543</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -11543,7 +11789,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>District facilities dept handles all campuses; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+          <t>Same campus address as Moss Point High; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -11554,8 +11800,149 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Moss Point Escatawpa Upper Elementary</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4208 Jamestown Rd</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>(228) 474-3300</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Moss Point SD; no email found; Source: web search - https://www.schooldigger.com/go/MS/zip/39563/search.aspx</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Moss Point High School</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4913 Weems St</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>(228) 475-5721</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Another listing gives (228) 475-5058; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Moss Point School District Office</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4924 Church St</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moss Point</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>39563</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>(228) 475-4558</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>District facilities dept handles all campuses; no email found; Source: web search - https://www.schooldigger.com/go/MS/district/03000/search.aspx</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M67"/>
+  <autoFilter ref="A1:M70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11762,7 +12149,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -11771,7 +12158,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -11876,7 +12263,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>42</v>
@@ -11885,7 +12272,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17"/>
@@ -11923,7 +12310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C19" t="n">
         <v>17</v>
@@ -11932,7 +12319,7 @@
         <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -11980,7 +12367,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
         <v>17</v>
@@ -11989,7 +12376,7 @@
         <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
@@ -11999,7 +12386,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C23" t="n">
         <v>25</v>
@@ -12008,7 +12395,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
